--- a/tests.xlsx
+++ b/tests.xlsx
@@ -8,22 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MaGa\Desktop\customs_test_bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FBEF4C-D47E-4FC9-86EA-14F894B2572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D867769-540F-4970-815F-E60C0A401AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="4020" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. test" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01. test'!$A$1:$G$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01. test'!$A$1:$G$435</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="2012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="2012">
   <si>
     <t>Божхона назоратининг шакллари неча турдан иборат?</t>
   </si>
@@ -6981,6 +6992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:XFC435"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7016,7 +7028,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7032,14 +7044,14 @@
       <c r="E2" s="1">
         <v>16</v>
       </c>
-      <c r="F2" s="1">
-        <v>2</v>
+      <c r="F2" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7055,14 +7067,14 @@
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1">
-        <v>3</v>
+      <c r="F3" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -7078,14 +7090,14 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>2</v>
+      <c r="F4" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -7101,14 +7113,14 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1">
-        <v>3</v>
+      <c r="F5" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -7124,14 +7136,14 @@
       <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="1">
-        <v>3</v>
+      <c r="F6" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -7147,14 +7159,14 @@
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="1">
-        <v>2</v>
+      <c r="F7" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -7170,14 +7182,14 @@
       <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1">
-        <v>4</v>
+      <c r="F8" t="s">
+        <v>2009</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -7193,14 +7205,14 @@
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="1">
-        <v>4</v>
+      <c r="F9" t="s">
+        <v>2009</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -7216,14 +7228,14 @@
       <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="1">
-        <v>2</v>
+      <c r="F10" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -7239,14 +7251,14 @@
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="1">
-        <v>2</v>
+      <c r="F11" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -7262,14 +7274,14 @@
       <c r="E12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="1">
-        <v>3</v>
+      <c r="F12" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -7285,14 +7297,14 @@
       <c r="E13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
+      <c r="F13" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -7308,14 +7320,14 @@
       <c r="E14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="1">
-        <v>2</v>
+      <c r="F14" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
@@ -7331,14 +7343,14 @@
       <c r="E15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="1">
-        <v>2</v>
+      <c r="F15" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>57</v>
       </c>
@@ -7354,14 +7366,14 @@
       <c r="E16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="1">
-        <v>1</v>
+      <c r="F16" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>62</v>
       </c>
@@ -7377,14 +7389,14 @@
       <c r="E17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="1">
-        <v>4</v>
+      <c r="F17" t="s">
+        <v>2009</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
@@ -7400,14 +7412,14 @@
       <c r="E18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="1">
-        <v>4</v>
+      <c r="F18" t="s">
+        <v>2009</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -7423,14 +7435,14 @@
       <c r="E19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="1">
-        <v>3</v>
+      <c r="F19" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>77</v>
       </c>
@@ -7446,14 +7458,14 @@
       <c r="E20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="1">
-        <v>2</v>
+      <c r="F20" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>78</v>
       </c>
@@ -7469,14 +7481,14 @@
       <c r="E21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="1">
-        <v>2</v>
+      <c r="F21" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
@@ -7492,14 +7504,14 @@
       <c r="E22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="1">
-        <v>4</v>
+      <c r="F22" t="s">
+        <v>2009</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
@@ -7515,14 +7527,14 @@
       <c r="E23" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="1">
-        <v>4</v>
+      <c r="F23" t="s">
+        <v>2009</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>94</v>
       </c>
@@ -7538,14 +7550,14 @@
       <c r="E24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="1">
-        <v>3</v>
+      <c r="F24" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>99</v>
       </c>
@@ -7561,14 +7573,14 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="1">
-        <v>3</v>
+      <c r="F25" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>100</v>
       </c>
@@ -7584,14 +7596,14 @@
       <c r="E26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="1">
-        <v>2</v>
+      <c r="F26" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>105</v>
       </c>
@@ -7607,14 +7619,14 @@
       <c r="E27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F27" s="1">
-        <v>3</v>
+      <c r="F27" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
@@ -7630,14 +7642,14 @@
       <c r="E28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="1">
-        <v>4</v>
+      <c r="F28" t="s">
+        <v>2009</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>115</v>
       </c>
@@ -7653,14 +7665,14 @@
       <c r="E29" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F29" s="1">
-        <v>2</v>
+      <c r="F29" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>120</v>
       </c>
@@ -7676,14 +7688,14 @@
       <c r="E30" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="1">
-        <v>3</v>
+      <c r="F30" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1884</v>
       </c>
@@ -7699,14 +7711,14 @@
       <c r="E31" s="1" t="s">
         <v>1888</v>
       </c>
-      <c r="F31" s="1">
-        <v>2</v>
+      <c r="F31" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>1889</v>
       </c>
@@ -7722,14 +7734,14 @@
       <c r="E32" s="1" t="s">
         <v>1893</v>
       </c>
-      <c r="F32" s="1">
-        <v>3</v>
+      <c r="F32" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>1894</v>
       </c>
@@ -7745,14 +7757,14 @@
       <c r="E33" s="1" t="s">
         <v>1898</v>
       </c>
-      <c r="F33" s="1">
-        <v>2</v>
+      <c r="F33" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1899</v>
       </c>
@@ -7768,14 +7780,14 @@
       <c r="E34" s="1" t="s">
         <v>1903</v>
       </c>
-      <c r="F34" s="1">
-        <v>2</v>
+      <c r="F34" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1904</v>
       </c>
@@ -7791,14 +7803,14 @@
       <c r="E35" s="1" t="s">
         <v>1908</v>
       </c>
-      <c r="F35" s="1">
-        <v>2</v>
+      <c r="F35" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>1909</v>
       </c>
@@ -7814,14 +7826,14 @@
       <c r="E36" s="1" t="s">
         <v>1913</v>
       </c>
-      <c r="F36" s="1">
-        <v>2</v>
+      <c r="F36" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>1914</v>
       </c>
@@ -7837,14 +7849,14 @@
       <c r="E37" s="1" t="s">
         <v>1918</v>
       </c>
-      <c r="F37" s="1">
-        <v>3</v>
+      <c r="F37" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>1919</v>
       </c>
@@ -7860,14 +7872,14 @@
       <c r="E38" s="1" t="s">
         <v>1923</v>
       </c>
-      <c r="F38" s="1">
-        <v>3</v>
+      <c r="F38" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>1924</v>
       </c>
@@ -7883,14 +7895,14 @@
       <c r="E39" s="1" t="s">
         <v>1926</v>
       </c>
-      <c r="F39" s="1">
-        <v>3</v>
+      <c r="F39" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>1927</v>
       </c>
@@ -7906,14 +7918,14 @@
       <c r="E40" s="1" t="s">
         <v>1931</v>
       </c>
-      <c r="F40" s="1">
-        <v>2</v>
+      <c r="F40" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>1932</v>
       </c>
@@ -7929,14 +7941,14 @@
       <c r="E41" s="1" t="s">
         <v>1935</v>
       </c>
-      <c r="F41" s="1">
-        <v>3</v>
+      <c r="F41" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>1936</v>
       </c>
@@ -7952,14 +7964,14 @@
       <c r="E42" s="1" t="s">
         <v>1940</v>
       </c>
-      <c r="F42" s="1">
-        <v>3</v>
+      <c r="F42" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>1941</v>
       </c>
@@ -7975,14 +7987,14 @@
       <c r="E43" s="1" t="s">
         <v>1937</v>
       </c>
-      <c r="F43" s="1">
-        <v>2</v>
+      <c r="F43" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>1945</v>
       </c>
@@ -7998,14 +8010,14 @@
       <c r="E44" s="1" t="s">
         <v>1947</v>
       </c>
-      <c r="F44" s="1">
-        <v>2</v>
+      <c r="F44" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>1948</v>
       </c>
@@ -8021,14 +8033,14 @@
       <c r="E45" s="1" t="s">
         <v>1952</v>
       </c>
-      <c r="F45" s="1">
-        <v>2</v>
+      <c r="F45" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>1953</v>
       </c>
@@ -8044,14 +8056,14 @@
       <c r="E46" s="1" t="s">
         <v>1957</v>
       </c>
-      <c r="F46" s="1">
-        <v>2</v>
+      <c r="F46" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>1958</v>
       </c>
@@ -8067,14 +8079,14 @@
       <c r="E47" s="1" t="s">
         <v>1962</v>
       </c>
-      <c r="F47" s="1">
-        <v>2</v>
+      <c r="F47" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>1963</v>
       </c>
@@ -8090,14 +8102,14 @@
       <c r="E48" s="1" t="s">
         <v>1965</v>
       </c>
-      <c r="F48" s="1">
-        <v>2</v>
+      <c r="F48" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>1966</v>
       </c>
@@ -8113,14 +8125,14 @@
       <c r="E49" s="1" t="s">
         <v>1970</v>
       </c>
-      <c r="F49" s="1">
-        <v>2</v>
+      <c r="F49" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>1971</v>
       </c>
@@ -8136,14 +8148,14 @@
       <c r="E50" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="F50" s="1">
-        <v>3</v>
+      <c r="F50" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>1972</v>
       </c>
@@ -8159,14 +8171,14 @@
       <c r="E51" s="1" t="s">
         <v>1976</v>
       </c>
-      <c r="F51" s="1">
-        <v>2</v>
+      <c r="F51" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>1977</v>
       </c>
@@ -8182,14 +8194,14 @@
       <c r="E52" s="3">
         <v>44866</v>
       </c>
-      <c r="F52" s="1">
-        <v>2</v>
+      <c r="F52" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>1978</v>
       </c>
@@ -8205,14 +8217,14 @@
       <c r="E53" s="1" t="s">
         <v>1982</v>
       </c>
-      <c r="F53" s="1">
-        <v>2</v>
+      <c r="F53" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>1983</v>
       </c>
@@ -8228,14 +8240,14 @@
       <c r="E54" s="1" t="s">
         <v>1984</v>
       </c>
-      <c r="F54" s="1">
-        <v>3</v>
+      <c r="F54" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>1985</v>
       </c>
@@ -8251,14 +8263,14 @@
       <c r="E55" s="1" t="s">
         <v>1986</v>
       </c>
-      <c r="F55" s="1">
-        <v>2</v>
+      <c r="F55" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>1987</v>
       </c>
@@ -8274,14 +8286,14 @@
       <c r="E56" s="1" t="s">
         <v>1991</v>
       </c>
-      <c r="F56" s="1">
-        <v>2</v>
+      <c r="F56" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>1992</v>
       </c>
@@ -8297,14 +8309,14 @@
       <c r="E57" s="1" t="s">
         <v>1996</v>
       </c>
-      <c r="F57" s="1">
-        <v>2</v>
+      <c r="F57" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>1997</v>
       </c>
@@ -8320,14 +8332,14 @@
       <c r="E58" s="1" t="s">
         <v>2001</v>
       </c>
-      <c r="F58" s="1">
-        <v>2</v>
+      <c r="F58" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>2002</v>
       </c>
@@ -8343,14 +8355,14 @@
       <c r="E59" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F59" s="1">
-        <v>2</v>
+      <c r="F59" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>2004</v>
       </c>
@@ -8366,14 +8378,14 @@
       <c r="E60" s="1" t="s">
         <v>1833</v>
       </c>
-      <c r="F60" s="1">
-        <v>3</v>
+      <c r="F60" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>125</v>
       </c>
@@ -8389,14 +8401,14 @@
       <c r="E61" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F61" s="1">
-        <v>1</v>
+      <c r="F61" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>131</v>
       </c>
@@ -8412,14 +8424,14 @@
       <c r="E62" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F62" s="1">
-        <v>3</v>
+      <c r="F62" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>136</v>
       </c>
@@ -8435,14 +8447,14 @@
       <c r="E63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F63" s="1">
-        <v>4</v>
+      <c r="F63" t="s">
+        <v>2009</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>141</v>
       </c>
@@ -8458,14 +8470,14 @@
       <c r="E64" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F64" s="1">
-        <v>2</v>
+      <c r="F64" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>146</v>
       </c>
@@ -8481,14 +8493,14 @@
       <c r="E65" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F65" s="1">
-        <v>2</v>
+      <c r="F65" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>151</v>
       </c>
@@ -8504,14 +8516,14 @@
       <c r="E66" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F66" s="1">
-        <v>3</v>
+      <c r="F66" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>156</v>
       </c>
@@ -8527,14 +8539,14 @@
       <c r="E67" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F67" s="1">
-        <v>3</v>
+      <c r="F67" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>161</v>
       </c>
@@ -8550,14 +8562,14 @@
       <c r="E68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F68" s="1">
-        <v>1</v>
+      <c r="F68" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>165</v>
       </c>
@@ -8573,14 +8585,14 @@
       <c r="E69" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F69" s="1">
-        <v>2</v>
+      <c r="F69" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>170</v>
       </c>
@@ -8596,14 +8608,14 @@
       <c r="E70" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F70" s="1">
-        <v>3</v>
+      <c r="F70" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>175</v>
       </c>
@@ -8619,14 +8631,14 @@
       <c r="E71" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F71" s="1">
-        <v>2</v>
+      <c r="F71" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>180</v>
       </c>
@@ -8642,14 +8654,14 @@
       <c r="E72" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F72" s="1">
-        <v>3</v>
+      <c r="F72" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>185</v>
       </c>
@@ -8665,14 +8677,14 @@
       <c r="E73" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F73" s="1">
-        <v>3</v>
+      <c r="F73" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>190</v>
       </c>
@@ -8688,14 +8700,14 @@
       <c r="E74" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F74" s="1">
-        <v>3</v>
+      <c r="F74" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>195</v>
       </c>
@@ -8711,14 +8723,14 @@
       <c r="E75" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F75" s="1">
-        <v>1</v>
+      <c r="F75" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>200</v>
       </c>
@@ -8734,14 +8746,14 @@
       <c r="E76" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F76" s="1">
-        <v>3</v>
+      <c r="F76" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>205</v>
       </c>
@@ -8757,14 +8769,14 @@
       <c r="E77" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F77" s="1">
-        <v>1</v>
+      <c r="F77" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>210</v>
       </c>
@@ -8780,14 +8792,14 @@
       <c r="E78" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F78" s="1">
-        <v>1</v>
+      <c r="F78" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>212</v>
       </c>
@@ -8803,14 +8815,14 @@
       <c r="E79" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F79" s="1">
-        <v>3</v>
+      <c r="F79" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>215</v>
       </c>
@@ -8826,14 +8838,14 @@
       <c r="E80" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F80" s="1">
-        <v>2</v>
+      <c r="F80" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>218</v>
       </c>
@@ -8849,14 +8861,14 @@
       <c r="E81" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F81" s="1">
-        <v>4</v>
+      <c r="F81" t="s">
+        <v>2009</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>222</v>
       </c>
@@ -8872,14 +8884,14 @@
       <c r="E82" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F82" s="1">
-        <v>2</v>
+      <c r="F82" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>226</v>
       </c>
@@ -8895,14 +8907,14 @@
       <c r="E83" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F83" s="1">
-        <v>3</v>
+      <c r="F83" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>231</v>
       </c>
@@ -8918,14 +8930,14 @@
       <c r="E84" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F84" s="1">
-        <v>2</v>
+      <c r="F84" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>236</v>
       </c>
@@ -8941,14 +8953,14 @@
       <c r="E85" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F85" s="1">
-        <v>4</v>
+      <c r="F85" t="s">
+        <v>2009</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>241</v>
       </c>
@@ -8964,14 +8976,14 @@
       <c r="E86" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F86" s="1">
-        <v>1</v>
+      <c r="F86" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>243</v>
       </c>
@@ -8987,14 +8999,14 @@
       <c r="E87" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F87" s="1">
-        <v>2</v>
+      <c r="F87" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>245</v>
       </c>
@@ -9010,14 +9022,14 @@
       <c r="E88" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F88" s="1">
-        <v>3</v>
+      <c r="F88" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>249</v>
       </c>
@@ -9033,14 +9045,14 @@
       <c r="E89" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F89" s="1">
-        <v>2</v>
+      <c r="F89" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>254</v>
       </c>
@@ -9056,14 +9068,14 @@
       <c r="E90" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F90" s="1">
-        <v>3</v>
+      <c r="F90" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>259</v>
       </c>
@@ -9079,14 +9091,14 @@
       <c r="E91" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F91" s="1">
-        <v>1</v>
+      <c r="F91" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>264</v>
       </c>
@@ -9102,14 +9114,14 @@
       <c r="E92" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F92" s="1">
-        <v>3</v>
+      <c r="F92" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>269</v>
       </c>
@@ -9125,14 +9137,14 @@
       <c r="E93" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F93" s="1">
-        <v>3</v>
+      <c r="F93" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>273</v>
       </c>
@@ -9148,14 +9160,14 @@
       <c r="E94" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F94" s="1">
-        <v>1</v>
+      <c r="F94" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>278</v>
       </c>
@@ -9171,14 +9183,14 @@
       <c r="E95" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F95" s="1">
-        <v>2</v>
+      <c r="F95" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>283</v>
       </c>
@@ -9194,14 +9206,14 @@
       <c r="E96" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F96" s="1">
-        <v>3</v>
+      <c r="F96" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>288</v>
       </c>
@@ -9217,14 +9229,14 @@
       <c r="E97" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F97" s="1">
-        <v>2</v>
+      <c r="F97" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>293</v>
       </c>
@@ -9240,14 +9252,14 @@
       <c r="E98" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F98" s="1">
-        <v>1</v>
+      <c r="F98" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>297</v>
       </c>
@@ -9263,14 +9275,14 @@
       <c r="E99" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F99" s="1">
-        <v>3</v>
+      <c r="F99" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>300</v>
       </c>
@@ -9286,14 +9298,14 @@
       <c r="E100" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F100" s="1">
-        <v>2</v>
+      <c r="F100" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>305</v>
       </c>
@@ -9309,14 +9321,14 @@
       <c r="E101" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F101" s="1">
-        <v>3</v>
+      <c r="F101" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>310</v>
       </c>
@@ -9332,14 +9344,14 @@
       <c r="E102" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F102" s="1">
-        <v>2</v>
+      <c r="F102" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>314</v>
       </c>
@@ -9355,14 +9367,14 @@
       <c r="E103" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F103" s="1">
-        <v>2</v>
+      <c r="F103" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>318</v>
       </c>
@@ -9378,14 +9390,14 @@
       <c r="E104" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F104" s="1">
-        <v>3</v>
+      <c r="F104" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>323</v>
       </c>
@@ -9401,14 +9413,14 @@
       <c r="E105" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F105" s="1">
-        <v>2</v>
+      <c r="F105" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>328</v>
       </c>
@@ -9424,14 +9436,14 @@
       <c r="E106" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="F106" s="1">
-        <v>3</v>
+      <c r="F106" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>333</v>
       </c>
@@ -9447,14 +9459,14 @@
       <c r="E107" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F107" s="1">
-        <v>4</v>
+      <c r="F107" t="s">
+        <v>2009</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>338</v>
       </c>
@@ -9470,14 +9482,14 @@
       <c r="E108" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F108" s="1">
-        <v>1</v>
+      <c r="F108" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>343</v>
       </c>
@@ -9493,14 +9505,14 @@
       <c r="E109" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F109" s="1">
-        <v>3</v>
+      <c r="F109" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>348</v>
       </c>
@@ -9516,14 +9528,14 @@
       <c r="E110" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F110" s="1">
-        <v>4</v>
+      <c r="F110" t="s">
+        <v>2009</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>352</v>
       </c>
@@ -9539,14 +9551,14 @@
       <c r="E111" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="F111" s="1">
-        <v>2</v>
+      <c r="F111" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>357</v>
       </c>
@@ -9562,14 +9574,14 @@
       <c r="E112" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F112" s="1">
-        <v>3</v>
+      <c r="F112" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>361</v>
       </c>
@@ -9585,14 +9597,14 @@
       <c r="E113" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="F113" s="1">
-        <v>3</v>
+      <c r="F113" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>366</v>
       </c>
@@ -9608,14 +9620,14 @@
       <c r="E114" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="F114" s="1">
-        <v>1</v>
+      <c r="F114" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>371</v>
       </c>
@@ -9631,14 +9643,14 @@
       <c r="E115" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F115" s="1">
-        <v>2</v>
+      <c r="F115" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>376</v>
       </c>
@@ -9654,14 +9666,14 @@
       <c r="E116" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F116" s="1">
-        <v>3</v>
+      <c r="F116" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>381</v>
       </c>
@@ -9677,14 +9689,14 @@
       <c r="E117" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F117" s="1">
-        <v>2</v>
+      <c r="F117" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>386</v>
       </c>
@@ -9700,14 +9712,14 @@
       <c r="E118" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="F118" s="1">
-        <v>1</v>
+      <c r="F118" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>391</v>
       </c>
@@ -9723,14 +9735,14 @@
       <c r="E119" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F119" s="1">
-        <v>3</v>
+      <c r="F119" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>396</v>
       </c>
@@ -9746,14 +9758,14 @@
       <c r="E120" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F120" s="1">
-        <v>4</v>
+      <c r="F120" t="s">
+        <v>2009</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>401</v>
       </c>
@@ -9769,14 +9781,14 @@
       <c r="E121" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F121" s="1">
-        <v>2</v>
+      <c r="F121" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>406</v>
       </c>
@@ -9792,14 +9804,14 @@
       <c r="E122" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F122" s="1">
-        <v>3</v>
+      <c r="F122" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>411</v>
       </c>
@@ -9815,14 +9827,14 @@
       <c r="E123" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F123" s="1">
-        <v>4</v>
+      <c r="F123" t="s">
+        <v>2009</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>416</v>
       </c>
@@ -9838,14 +9850,14 @@
       <c r="E124" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="F124" s="1">
-        <v>3</v>
+      <c r="F124" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>421</v>
       </c>
@@ -9861,14 +9873,14 @@
       <c r="E125" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F125" s="1">
-        <v>2</v>
+      <c r="F125" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>426</v>
       </c>
@@ -9884,14 +9896,14 @@
       <c r="E126" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F126" s="1">
-        <v>2</v>
+      <c r="F126" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>431</v>
       </c>
@@ -9907,14 +9919,14 @@
       <c r="E127" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F127" s="1">
-        <v>4</v>
+      <c r="F127" t="s">
+        <v>2009</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>433</v>
       </c>
@@ -9930,14 +9942,14 @@
       <c r="E128" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="F128" s="1">
-        <v>1</v>
+      <c r="F128" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>438</v>
       </c>
@@ -9953,14 +9965,14 @@
       <c r="E129" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F129" s="1">
-        <v>2</v>
+      <c r="F129" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>443</v>
       </c>
@@ -9976,14 +9988,14 @@
       <c r="E130" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F130" s="1">
-        <v>4</v>
+      <c r="F130" t="s">
+        <v>2009</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>421</v>
       </c>
@@ -9999,14 +10011,14 @@
       <c r="E131" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F131" s="1">
-        <v>3</v>
+      <c r="F131" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>451</v>
       </c>
@@ -10022,14 +10034,14 @@
       <c r="E132" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F132" s="1">
-        <v>4</v>
+      <c r="F132" t="s">
+        <v>2009</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>455</v>
       </c>
@@ -10045,14 +10057,14 @@
       <c r="E133" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="F133" s="1">
-        <v>3</v>
+      <c r="F133" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>460</v>
       </c>
@@ -10068,14 +10080,14 @@
       <c r="E134" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="F134" s="1">
-        <v>3</v>
+      <c r="F134" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>466</v>
       </c>
@@ -10091,14 +10103,14 @@
       <c r="E135" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F135" s="1">
-        <v>4</v>
+      <c r="F135" t="s">
+        <v>2009</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>471</v>
       </c>
@@ -10114,14 +10126,14 @@
       <c r="E136" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F136" s="1">
-        <v>3</v>
+      <c r="F136" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>476</v>
       </c>
@@ -10137,14 +10149,14 @@
       <c r="E137" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F137" s="1">
-        <v>4</v>
+      <c r="F137" t="s">
+        <v>2009</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>481</v>
       </c>
@@ -10160,14 +10172,14 @@
       <c r="E138" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="F138" s="1">
-        <v>2</v>
+      <c r="F138" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>486</v>
       </c>
@@ -10183,14 +10195,14 @@
       <c r="E139" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F139" s="1">
-        <v>2</v>
+      <c r="F139" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>491</v>
       </c>
@@ -10206,14 +10218,14 @@
       <c r="E140" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F140" s="1">
-        <v>3</v>
+      <c r="F140" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>496</v>
       </c>
@@ -10229,14 +10241,14 @@
       <c r="E141" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F141" s="1">
-        <v>1</v>
+      <c r="F141" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>500</v>
       </c>
@@ -10252,14 +10264,14 @@
       <c r="E142" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="F142" s="1">
-        <v>3</v>
+      <c r="F142" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>504</v>
       </c>
@@ -10275,14 +10287,14 @@
       <c r="E143" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F143" s="1">
-        <v>4</v>
+      <c r="F143" t="s">
+        <v>2009</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>509</v>
       </c>
@@ -10298,14 +10310,14 @@
       <c r="E144" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F144" s="1">
-        <v>4</v>
+      <c r="F144" t="s">
+        <v>2009</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>514</v>
       </c>
@@ -10321,14 +10333,14 @@
       <c r="E145" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="F145" s="1">
-        <v>2</v>
+      <c r="F145" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>519</v>
       </c>
@@ -10344,14 +10356,14 @@
       <c r="E146" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="F146" s="1">
-        <v>3</v>
+      <c r="F146" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>522</v>
       </c>
@@ -10367,14 +10379,14 @@
       <c r="E147" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="F147" s="1">
-        <v>4</v>
+      <c r="F147" t="s">
+        <v>2009</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>526</v>
       </c>
@@ -10390,14 +10402,14 @@
       <c r="E148" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="F148" s="1">
-        <v>2</v>
+      <c r="F148" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>531</v>
       </c>
@@ -10413,14 +10425,14 @@
       <c r="E149" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F149" s="1">
-        <v>1</v>
+      <c r="F149" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>534</v>
       </c>
@@ -10436,14 +10448,14 @@
       <c r="E150" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="F150" s="1">
-        <v>3</v>
+      <c r="F150" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>539</v>
       </c>
@@ -10459,14 +10471,14 @@
       <c r="E151" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F151" s="1">
-        <v>3</v>
+      <c r="F151" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>544</v>
       </c>
@@ -10482,14 +10494,14 @@
       <c r="E152" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F152" s="1">
-        <v>2</v>
+      <c r="F152" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>549</v>
       </c>
@@ -10505,14 +10517,14 @@
       <c r="E153" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F153" s="1">
-        <v>4</v>
+      <c r="F153" t="s">
+        <v>2009</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>553</v>
       </c>
@@ -10528,14 +10540,14 @@
       <c r="E154" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F154" s="1">
-        <v>3</v>
+      <c r="F154" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>557</v>
       </c>
@@ -10551,14 +10563,14 @@
       <c r="E155" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="F155" s="1">
-        <v>1</v>
+      <c r="F155" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>562</v>
       </c>
@@ -10574,14 +10586,14 @@
       <c r="E156" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="F156" s="1">
-        <v>2</v>
+      <c r="F156" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>567</v>
       </c>
@@ -10597,14 +10609,14 @@
       <c r="E157" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F157" s="1">
-        <v>4</v>
+      <c r="F157" t="s">
+        <v>2009</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>571</v>
       </c>
@@ -10620,8 +10632,8 @@
       <c r="E158" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="F158" s="1">
-        <v>1</v>
+      <c r="F158" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G158" s="1"/>
     </row>
@@ -10646,7 +10658,7 @@
       </c>
       <c r="G159" s="2"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>579</v>
       </c>
@@ -10662,14 +10674,14 @@
       <c r="E160" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="F160" s="1">
-        <v>2</v>
+      <c r="F160" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>584</v>
       </c>
@@ -10685,14 +10697,14 @@
       <c r="E161" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="F161" s="1">
-        <v>4</v>
+      <c r="F161" t="s">
+        <v>2009</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>588</v>
       </c>
@@ -10708,14 +10720,14 @@
       <c r="E162" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="F162" s="1">
-        <v>1</v>
+      <c r="F162" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>593</v>
       </c>
@@ -10731,14 +10743,14 @@
       <c r="E163" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F163" s="1">
-        <v>3</v>
+      <c r="F163" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>598</v>
       </c>
@@ -10754,14 +10766,14 @@
       <c r="E164" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="F164" s="1">
-        <v>3</v>
+      <c r="F164" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>603</v>
       </c>
@@ -10777,14 +10789,14 @@
       <c r="E165" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F165" s="1">
-        <v>3</v>
+      <c r="F165" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>608</v>
       </c>
@@ -10800,14 +10812,14 @@
       <c r="E166" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="F166" s="1">
-        <v>5</v>
+      <c r="F166" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>610</v>
       </c>
@@ -10823,14 +10835,14 @@
       <c r="E167" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="F167" s="1">
-        <v>2</v>
+      <c r="F167" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>639</v>
       </c>
@@ -10846,14 +10858,14 @@
       <c r="E168" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="F168" s="1">
-        <v>2</v>
+      <c r="F168" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>644</v>
       </c>
@@ -10869,14 +10881,14 @@
       <c r="E169" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="F169" s="1">
-        <v>2</v>
+      <c r="F169" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>649</v>
       </c>
@@ -10892,14 +10904,14 @@
       <c r="E170" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="F170" s="1">
-        <v>4</v>
+      <c r="F170" t="s">
+        <v>2009</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>654</v>
       </c>
@@ -10915,14 +10927,14 @@
       <c r="E171" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="F171" s="1">
-        <v>3</v>
+      <c r="F171" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>659</v>
       </c>
@@ -10938,14 +10950,14 @@
       <c r="E172" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F172" s="1">
-        <v>3</v>
+      <c r="F172" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>661</v>
       </c>
@@ -10961,14 +10973,14 @@
       <c r="E173" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="F173" s="1">
-        <v>3</v>
+      <c r="F173" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>666</v>
       </c>
@@ -10984,14 +10996,14 @@
       <c r="E174" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="F174" s="1">
-        <v>2</v>
+      <c r="F174" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>668</v>
       </c>
@@ -11007,14 +11019,14 @@
       <c r="E175" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F175" s="1">
-        <v>4</v>
+      <c r="F175" t="s">
+        <v>2009</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>674</v>
       </c>
@@ -11030,14 +11042,14 @@
       <c r="E176" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F176" s="1">
-        <v>3</v>
+      <c r="F176" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>678</v>
       </c>
@@ -11053,14 +11065,14 @@
       <c r="E177" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="F177" s="1">
-        <v>2</v>
+      <c r="F177" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>719</v>
       </c>
@@ -11076,14 +11088,14 @@
       <c r="E178" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F178" s="1">
-        <v>1</v>
+      <c r="F178" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>724</v>
       </c>
@@ -11099,14 +11111,14 @@
       <c r="E179" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="F179" s="1">
-        <v>2</v>
+      <c r="F179" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>728</v>
       </c>
@@ -11122,14 +11134,14 @@
       <c r="E180" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="F180" s="1">
-        <v>1</v>
+      <c r="F180" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>729</v>
       </c>
@@ -11145,14 +11157,14 @@
       <c r="E181" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="F181" s="1">
-        <v>3</v>
+      <c r="F181" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>734</v>
       </c>
@@ -11168,14 +11180,14 @@
       <c r="E182" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="F182" s="1">
-        <v>1</v>
+      <c r="F182" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>739</v>
       </c>
@@ -11191,14 +11203,14 @@
       <c r="E183" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F183" s="1">
-        <v>1</v>
+      <c r="F183" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>744</v>
       </c>
@@ -11214,14 +11226,14 @@
       <c r="E184" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F184" s="1">
-        <v>2</v>
+      <c r="F184" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>745</v>
       </c>
@@ -11237,14 +11249,14 @@
       <c r="E185" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F185" s="1">
-        <v>3</v>
+      <c r="F185" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>746</v>
       </c>
@@ -11260,14 +11272,14 @@
       <c r="E186" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F186" s="1">
-        <v>3</v>
+      <c r="F186" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>747</v>
       </c>
@@ -11283,14 +11295,14 @@
       <c r="E187" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F187" s="1">
-        <v>3</v>
+      <c r="F187" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>748</v>
       </c>
@@ -11306,14 +11318,14 @@
       <c r="E188" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F188" s="1">
-        <v>4</v>
+      <c r="F188" t="s">
+        <v>2009</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>749</v>
       </c>
@@ -11329,14 +11341,14 @@
       <c r="E189" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="F189" s="1">
-        <v>3</v>
+      <c r="F189" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>754</v>
       </c>
@@ -11352,14 +11364,14 @@
       <c r="E190" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="F190" s="1">
-        <v>2</v>
+      <c r="F190" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>759</v>
       </c>
@@ -11375,14 +11387,14 @@
       <c r="E191" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="F191" s="1">
-        <v>3</v>
+      <c r="F191" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>764</v>
       </c>
@@ -11398,14 +11410,14 @@
       <c r="E192" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="F192" s="1">
-        <v>2</v>
+      <c r="F192" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>769</v>
       </c>
@@ -11421,14 +11433,14 @@
       <c r="E193" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="F193" s="1">
-        <v>1</v>
+      <c r="F193" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>774</v>
       </c>
@@ -11444,14 +11456,14 @@
       <c r="E194" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="F194" s="1">
-        <v>1</v>
+      <c r="F194" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>779</v>
       </c>
@@ -11467,14 +11479,14 @@
       <c r="E195" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="F195" s="1">
-        <v>2</v>
+      <c r="F195" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>615</v>
       </c>
@@ -11490,14 +11502,14 @@
       <c r="E196" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="F196" s="1">
-        <v>1</v>
+      <c r="F196" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>620</v>
       </c>
@@ -11513,14 +11525,14 @@
       <c r="E197" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="F197" s="1">
-        <v>4</v>
+      <c r="F197" t="s">
+        <v>2009</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>630</v>
       </c>
@@ -11536,14 +11548,14 @@
       <c r="E198" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="F198" s="1">
-        <v>4</v>
+      <c r="F198" t="s">
+        <v>2009</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>634</v>
       </c>
@@ -11559,14 +11571,14 @@
       <c r="E199" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="F199" s="1">
-        <v>1</v>
+      <c r="F199" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>782</v>
       </c>
@@ -11582,14 +11594,14 @@
       <c r="E200" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="F200" s="1">
-        <v>2</v>
+      <c r="F200" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>787</v>
       </c>
@@ -11605,14 +11617,14 @@
       <c r="E201" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="F201" s="1">
-        <v>1</v>
+      <c r="F201" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>792</v>
       </c>
@@ -11628,14 +11640,14 @@
       <c r="E202" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="F202" s="1">
-        <v>1</v>
+      <c r="F202" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>797</v>
       </c>
@@ -11651,14 +11663,14 @@
       <c r="E203" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="F203" s="1">
-        <v>4</v>
+      <c r="F203" t="s">
+        <v>2009</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>802</v>
       </c>
@@ -11674,14 +11686,14 @@
       <c r="E204" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="F204" s="1">
-        <v>2</v>
+      <c r="F204" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>806</v>
       </c>
@@ -11697,14 +11709,14 @@
       <c r="E205" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="F205" s="1">
-        <v>2</v>
+      <c r="F205" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>811</v>
       </c>
@@ -11720,14 +11732,14 @@
       <c r="E206" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="F206" s="1">
-        <v>1</v>
+      <c r="F206" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>816</v>
       </c>
@@ -11743,14 +11755,14 @@
       <c r="E207" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="F207" s="1">
-        <v>3</v>
+      <c r="F207" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>821</v>
       </c>
@@ -11766,14 +11778,14 @@
       <c r="E208" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="F208" s="1">
-        <v>3</v>
+      <c r="F208" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>826</v>
       </c>
@@ -11789,14 +11801,14 @@
       <c r="E209" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="F209" s="1">
-        <v>1</v>
+      <c r="F209" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>829</v>
       </c>
@@ -11812,14 +11824,14 @@
       <c r="E210" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="F210" s="1">
-        <v>1</v>
+      <c r="F210" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>834</v>
       </c>
@@ -11835,14 +11847,14 @@
       <c r="E211" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="F211" s="1">
-        <v>2</v>
+      <c r="F211" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>836</v>
       </c>
@@ -11858,14 +11870,14 @@
       <c r="E212" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="F212" s="1">
-        <v>1</v>
+      <c r="F212" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>841</v>
       </c>
@@ -11881,14 +11893,14 @@
       <c r="E213" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="F213" s="1">
-        <v>3</v>
+      <c r="F213" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>845</v>
       </c>
@@ -11904,14 +11916,14 @@
       <c r="E214" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="F214" s="1">
-        <v>2</v>
+      <c r="F214" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>850</v>
       </c>
@@ -11927,14 +11939,14 @@
       <c r="E215" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="F215" s="1">
-        <v>4</v>
+      <c r="F215" t="s">
+        <v>2009</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>855</v>
       </c>
@@ -11950,14 +11962,14 @@
       <c r="E216" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="F216" s="1">
-        <v>2</v>
+      <c r="F216" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>860</v>
       </c>
@@ -11973,14 +11985,14 @@
       <c r="E217" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="F217" s="1">
-        <v>3</v>
+      <c r="F217" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>865</v>
       </c>
@@ -11996,14 +12008,14 @@
       <c r="E218" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="F218" s="1">
-        <v>1</v>
+      <c r="F218" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>870</v>
       </c>
@@ -12019,14 +12031,14 @@
       <c r="E219" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="F219" s="1">
-        <v>2</v>
+      <c r="F219" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>875</v>
       </c>
@@ -12042,14 +12054,14 @@
       <c r="E220" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="F220" s="1">
-        <v>1</v>
+      <c r="F220" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>880</v>
       </c>
@@ -12065,14 +12077,14 @@
       <c r="E221" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="F221" s="1">
-        <v>2</v>
+      <c r="F221" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>885</v>
       </c>
@@ -12088,14 +12100,14 @@
       <c r="E222" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="F222" s="1">
-        <v>3</v>
+      <c r="F222" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>890</v>
       </c>
@@ -12111,14 +12123,14 @@
       <c r="E223" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F223" s="1">
-        <v>3</v>
+      <c r="F223" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>894</v>
       </c>
@@ -12134,14 +12146,14 @@
       <c r="E224" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="F224" s="1">
-        <v>4</v>
+      <c r="F224" t="s">
+        <v>2009</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>897</v>
       </c>
@@ -12157,14 +12169,14 @@
       <c r="E225" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="F225" s="1">
-        <v>2</v>
+      <c r="F225" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>902</v>
       </c>
@@ -12180,14 +12192,14 @@
       <c r="E226" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="F226" s="1">
-        <v>1</v>
+      <c r="F226" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>907</v>
       </c>
@@ -12203,14 +12215,14 @@
       <c r="E227" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="F227" s="1">
-        <v>1</v>
+      <c r="F227" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>912</v>
       </c>
@@ -12226,14 +12238,14 @@
       <c r="E228" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="F228" s="1">
-        <v>3</v>
+      <c r="F228" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>917</v>
       </c>
@@ -12249,14 +12261,14 @@
       <c r="E229" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="F229" s="1">
-        <v>2</v>
+      <c r="F229" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>922</v>
       </c>
@@ -12272,14 +12284,14 @@
       <c r="E230" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="F230" s="1">
-        <v>1</v>
+      <c r="F230" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>927</v>
       </c>
@@ -12295,14 +12307,14 @@
       <c r="E231" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="F231" s="1">
-        <v>1</v>
+      <c r="F231" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>932</v>
       </c>
@@ -12318,14 +12330,14 @@
       <c r="E232" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="F232" s="1">
-        <v>2</v>
+      <c r="F232" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>937</v>
       </c>
@@ -12341,14 +12353,14 @@
       <c r="E233" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="F233" s="1">
-        <v>2</v>
+      <c r="F233" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>942</v>
       </c>
@@ -12364,14 +12376,14 @@
       <c r="E234" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="F234" s="1">
-        <v>3</v>
+      <c r="F234" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>947</v>
       </c>
@@ -12387,14 +12399,14 @@
       <c r="E235" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="F235" s="1">
-        <v>3</v>
+      <c r="F235" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>952</v>
       </c>
@@ -12410,14 +12422,14 @@
       <c r="E236" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="F236" s="1">
-        <v>2</v>
+      <c r="F236" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>957</v>
       </c>
@@ -12433,14 +12445,14 @@
       <c r="E237" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="F237" s="1">
-        <v>3</v>
+      <c r="F237" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>962</v>
       </c>
@@ -12456,14 +12468,14 @@
       <c r="E238" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="F238" s="1">
-        <v>1</v>
+      <c r="F238" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>967</v>
       </c>
@@ -12479,14 +12491,14 @@
       <c r="E239" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="F239" s="1">
-        <v>4</v>
+      <c r="F239" t="s">
+        <v>2009</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>972</v>
       </c>
@@ -12502,14 +12514,14 @@
       <c r="E240" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="F240" s="1">
-        <v>3</v>
+      <c r="F240" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>977</v>
       </c>
@@ -12525,14 +12537,14 @@
       <c r="E241" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="F241" s="1">
-        <v>4</v>
+      <c r="F241" t="s">
+        <v>2009</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>683</v>
       </c>
@@ -12548,14 +12560,14 @@
       <c r="E242" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="F242" s="1">
-        <v>3</v>
+      <c r="F242" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>687</v>
       </c>
@@ -12571,14 +12583,14 @@
       <c r="E243" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="F243" s="1">
-        <v>4</v>
+      <c r="F243" t="s">
+        <v>2009</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>692</v>
       </c>
@@ -12594,14 +12606,14 @@
       <c r="E244" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="F244" s="1">
-        <v>2</v>
+      <c r="F244" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>697</v>
       </c>
@@ -12617,14 +12629,14 @@
       <c r="E245" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="F245" s="1">
-        <v>4</v>
+      <c r="F245" t="s">
+        <v>2009</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>702</v>
       </c>
@@ -12640,14 +12652,14 @@
       <c r="E246" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="F246" s="1">
-        <v>2</v>
+      <c r="F246" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>707</v>
       </c>
@@ -12663,14 +12675,14 @@
       <c r="E247" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="F247" s="1">
-        <v>3</v>
+      <c r="F247" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>712</v>
       </c>
@@ -12686,14 +12698,14 @@
       <c r="E248" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="F248" s="1">
-        <v>4</v>
+      <c r="F248" t="s">
+        <v>2009</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>625</v>
       </c>
@@ -12709,14 +12721,14 @@
       <c r="E249" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="F249" s="1">
-        <v>1</v>
+      <c r="F249" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>1026</v>
       </c>
@@ -12732,14 +12744,14 @@
       <c r="E250" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="F250" s="1">
-        <v>3</v>
+      <c r="F250" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>1027</v>
       </c>
@@ -12755,14 +12767,14 @@
       <c r="E251" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="F251" s="1">
-        <v>2</v>
+      <c r="F251" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>990</v>
       </c>
@@ -12778,14 +12790,14 @@
       <c r="E252" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="F252" s="1">
-        <v>4</v>
+      <c r="F252" t="s">
+        <v>2009</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>995</v>
       </c>
@@ -12801,14 +12813,14 @@
       <c r="E253" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="F253" s="1">
-        <v>1</v>
+      <c r="F253" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>1028</v>
       </c>
@@ -12824,14 +12836,14 @@
       <c r="E254" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="F254" s="1">
-        <v>3</v>
+      <c r="F254" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>1029</v>
       </c>
@@ -12847,14 +12859,14 @@
       <c r="E255" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="F255" s="1">
-        <v>2</v>
+      <c r="F255" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>1030</v>
       </c>
@@ -12870,14 +12882,14 @@
       <c r="E256" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="F256" s="1">
-        <v>4</v>
+      <c r="F256" t="s">
+        <v>2009</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>1031</v>
       </c>
@@ -12893,14 +12905,14 @@
       <c r="E257" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="F257" s="1">
-        <v>3</v>
+      <c r="F257" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>1032</v>
       </c>
@@ -12916,14 +12928,14 @@
       <c r="E258" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="F258" s="1">
-        <v>3</v>
+      <c r="F258" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>1033</v>
       </c>
@@ -12939,14 +12951,14 @@
       <c r="E259" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="F259" s="1">
-        <v>3</v>
+      <c r="F259" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1034</v>
       </c>
@@ -12962,14 +12974,14 @@
       <c r="E260" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="F260" s="1">
-        <v>2</v>
+      <c r="F260" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>1035</v>
       </c>
@@ -12985,14 +12997,14 @@
       <c r="E261" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="F261" s="1">
-        <v>3</v>
+      <c r="F261" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>1040</v>
       </c>
@@ -13008,14 +13020,14 @@
       <c r="E262" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="F262" s="1">
-        <v>4</v>
+      <c r="F262" t="s">
+        <v>2009</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>1046</v>
       </c>
@@ -13031,14 +13043,14 @@
       <c r="E263" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="F263" s="1">
-        <v>3</v>
+      <c r="F263" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>1051</v>
       </c>
@@ -13054,14 +13066,14 @@
       <c r="E264" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F264" s="1">
-        <v>1</v>
+      <c r="F264" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>1055</v>
       </c>
@@ -13077,14 +13089,14 @@
       <c r="E265" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="F265" s="1">
-        <v>4</v>
+      <c r="F265" t="s">
+        <v>2009</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>1060</v>
       </c>
@@ -13100,14 +13112,14 @@
       <c r="E266" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="F266" s="1">
-        <v>3</v>
+      <c r="F266" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>1065</v>
       </c>
@@ -13123,14 +13135,14 @@
       <c r="E267" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="F267" s="1">
-        <v>3</v>
+      <c r="F267" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>1070</v>
       </c>
@@ -13146,14 +13158,14 @@
       <c r="E268" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="F268" s="1">
-        <v>2</v>
+      <c r="F268" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>1075</v>
       </c>
@@ -13169,14 +13181,14 @@
       <c r="E269" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="F269" s="1">
-        <v>2</v>
+      <c r="F269" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>1080</v>
       </c>
@@ -13192,14 +13204,14 @@
       <c r="E270" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="F270" s="1">
-        <v>3</v>
+      <c r="F270" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>1085</v>
       </c>
@@ -13215,14 +13227,14 @@
       <c r="E271" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="F271" s="1">
-        <v>4</v>
+      <c r="F271" t="s">
+        <v>2009</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>1090</v>
       </c>
@@ -13238,14 +13250,14 @@
       <c r="E272" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="F272" s="1">
-        <v>3</v>
+      <c r="F272" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>1095</v>
       </c>
@@ -13261,14 +13273,14 @@
       <c r="E273" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="F273" s="1">
-        <v>2</v>
+      <c r="F273" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>1099</v>
       </c>
@@ -13284,14 +13296,14 @@
       <c r="E274" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="F274" s="1">
-        <v>3</v>
+      <c r="F274" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>1104</v>
       </c>
@@ -13307,14 +13319,14 @@
       <c r="E275" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="F275" s="1">
-        <v>4</v>
+      <c r="F275" t="s">
+        <v>2009</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>1109</v>
       </c>
@@ -13330,14 +13342,14 @@
       <c r="E276" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="F276" s="1">
-        <v>3</v>
+      <c r="F276" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>1114</v>
       </c>
@@ -13353,14 +13365,14 @@
       <c r="E277" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="F277" s="1">
-        <v>2</v>
+      <c r="F277" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>1119</v>
       </c>
@@ -13376,14 +13388,14 @@
       <c r="E278" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="F278" s="1">
-        <v>2</v>
+      <c r="F278" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>1123</v>
       </c>
@@ -13399,14 +13411,14 @@
       <c r="E279" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="F279" s="1">
-        <v>3</v>
+      <c r="F279" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>1126</v>
       </c>
@@ -13422,14 +13434,14 @@
       <c r="E280" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="F280" s="1">
-        <v>4</v>
+      <c r="F280" t="s">
+        <v>2009</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>1131</v>
       </c>
@@ -13445,14 +13457,14 @@
       <c r="E281" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="F281" s="1">
-        <v>2</v>
+      <c r="F281" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>1136</v>
       </c>
@@ -13468,14 +13480,14 @@
       <c r="E282" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="F282" s="1">
-        <v>1</v>
+      <c r="F282" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>1141</v>
       </c>
@@ -13491,14 +13503,14 @@
       <c r="E283" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="F283" s="1">
-        <v>4</v>
+      <c r="F283" t="s">
+        <v>2009</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>1146</v>
       </c>
@@ -13514,14 +13526,14 @@
       <c r="E284" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="F284" s="1">
-        <v>3</v>
+      <c r="F284" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>1150</v>
       </c>
@@ -13537,14 +13549,14 @@
       <c r="E285" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="F285" s="1">
-        <v>4</v>
+      <c r="F285" t="s">
+        <v>2009</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1155</v>
       </c>
@@ -13560,14 +13572,14 @@
       <c r="E286" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="F286" s="1">
-        <v>2</v>
+      <c r="F286" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1160</v>
       </c>
@@ -13583,14 +13595,14 @@
       <c r="E287" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="F287" s="1">
-        <v>2</v>
+      <c r="F287" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1165</v>
       </c>
@@ -13606,14 +13618,14 @@
       <c r="E288" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="F288" s="1">
-        <v>3</v>
+      <c r="F288" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1170</v>
       </c>
@@ -13629,14 +13641,14 @@
       <c r="E289" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="F289" s="1">
-        <v>4</v>
+      <c r="F289" t="s">
+        <v>2009</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1175</v>
       </c>
@@ -13652,14 +13664,14 @@
       <c r="E290" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="F290" s="1">
-        <v>2</v>
+      <c r="F290" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1180</v>
       </c>
@@ -13675,14 +13687,14 @@
       <c r="E291" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="F291" s="1">
-        <v>1</v>
+      <c r="F291" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1185</v>
       </c>
@@ -13698,14 +13710,14 @@
       <c r="E292" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="F292" s="1">
-        <v>2</v>
+      <c r="F292" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1190</v>
       </c>
@@ -13721,14 +13733,14 @@
       <c r="E293" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="F293" s="1">
-        <v>3</v>
+      <c r="F293" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1195</v>
       </c>
@@ -13744,14 +13756,14 @@
       <c r="E294" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="F294" s="1">
-        <v>4</v>
+      <c r="F294" t="s">
+        <v>2009</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1200</v>
       </c>
@@ -13767,14 +13779,14 @@
       <c r="E295" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="F295" s="1">
-        <v>2</v>
+      <c r="F295" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1205</v>
       </c>
@@ -13790,14 +13802,14 @@
       <c r="E296" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="F296" s="1">
-        <v>3</v>
+      <c r="F296" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1210</v>
       </c>
@@ -13813,14 +13825,14 @@
       <c r="E297" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="F297" s="1">
-        <v>4</v>
+      <c r="F297" t="s">
+        <v>2009</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>1215</v>
       </c>
@@ -13836,14 +13848,14 @@
       <c r="E298" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="F298" s="1">
-        <v>2</v>
+      <c r="F298" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>1220</v>
       </c>
@@ -13859,14 +13871,14 @@
       <c r="E299" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="F299" s="1">
-        <v>1</v>
+      <c r="F299" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>1225</v>
       </c>
@@ -13882,14 +13894,14 @@
       <c r="E300" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="F300" s="1">
-        <v>3</v>
+      <c r="F300" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>1229</v>
       </c>
@@ -13905,14 +13917,14 @@
       <c r="E301" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="F301" s="1">
-        <v>2</v>
+      <c r="F301" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>1234</v>
       </c>
@@ -13928,14 +13940,14 @@
       <c r="E302" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="F302" s="1">
-        <v>4</v>
+      <c r="F302" t="s">
+        <v>2009</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>1239</v>
       </c>
@@ -13951,14 +13963,14 @@
       <c r="E303" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="F303" s="1">
-        <v>2</v>
+      <c r="F303" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>1244</v>
       </c>
@@ -13974,14 +13986,14 @@
       <c r="E304" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="F304" s="1">
-        <v>4</v>
+      <c r="F304" t="s">
+        <v>2009</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1249</v>
       </c>
@@ -13997,14 +14009,14 @@
       <c r="E305" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="F305" s="1">
-        <v>3</v>
+      <c r="F305" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>1254</v>
       </c>
@@ -14020,14 +14032,14 @@
       <c r="E306" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="F306" s="1">
-        <v>4</v>
+      <c r="F306" t="s">
+        <v>2009</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>1260</v>
       </c>
@@ -14043,14 +14055,14 @@
       <c r="E307" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="F307" s="1">
-        <v>4</v>
+      <c r="F307" t="s">
+        <v>2009</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1265</v>
       </c>
@@ -14066,14 +14078,14 @@
       <c r="E308" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="F308" s="1">
-        <v>1</v>
+      <c r="F308" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1270</v>
       </c>
@@ -14089,14 +14101,14 @@
       <c r="E309" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="F309" s="1">
-        <v>2</v>
+      <c r="F309" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1275</v>
       </c>
@@ -14112,14 +14124,14 @@
       <c r="E310" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="F310" s="1">
-        <v>3</v>
+      <c r="F310" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1280</v>
       </c>
@@ -14135,14 +14147,14 @@
       <c r="E311" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="F311" s="1">
-        <v>3</v>
+      <c r="F311" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1285</v>
       </c>
@@ -14158,14 +14170,14 @@
       <c r="E312" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F312" s="1">
-        <v>3</v>
+      <c r="F312" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1289</v>
       </c>
@@ -14181,14 +14193,14 @@
       <c r="E313" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="F313" s="1">
-        <v>1</v>
+      <c r="F313" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1293</v>
       </c>
@@ -14204,14 +14216,14 @@
       <c r="E314" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="F314" s="1">
-        <v>2</v>
+      <c r="F314" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1298</v>
       </c>
@@ -14227,14 +14239,14 @@
       <c r="E315" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="F315" s="1">
-        <v>1</v>
+      <c r="F315" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1301</v>
       </c>
@@ -14250,14 +14262,14 @@
       <c r="E316" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="F316" s="1">
-        <v>2</v>
+      <c r="F316" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1306</v>
       </c>
@@ -14273,14 +14285,14 @@
       <c r="E317" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="F317" s="1">
-        <v>2</v>
+      <c r="F317" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1311</v>
       </c>
@@ -14296,14 +14308,14 @@
       <c r="E318" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="F318" s="1">
-        <v>2</v>
+      <c r="F318" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1316</v>
       </c>
@@ -14319,14 +14331,14 @@
       <c r="E319" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="F319" s="1">
-        <v>3</v>
+      <c r="F319" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1321</v>
       </c>
@@ -14342,14 +14354,14 @@
       <c r="E320" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="F320" s="1">
-        <v>3</v>
+      <c r="F320" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1324</v>
       </c>
@@ -14365,14 +14377,14 @@
       <c r="E321" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="F321" s="1">
-        <v>4</v>
+      <c r="F321" t="s">
+        <v>2009</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1327</v>
       </c>
@@ -14388,14 +14400,14 @@
       <c r="E322" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="F322" s="1">
-        <v>3</v>
+      <c r="F322" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1332</v>
       </c>
@@ -14411,14 +14423,14 @@
       <c r="E323" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="F323" s="1">
-        <v>3</v>
+      <c r="F323" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1337</v>
       </c>
@@ -14434,14 +14446,14 @@
       <c r="E324" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="F324" s="1">
-        <v>4</v>
+      <c r="F324" t="s">
+        <v>2009</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1343</v>
       </c>
@@ -14457,14 +14469,14 @@
       <c r="E325" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="F325" s="1">
-        <v>3</v>
+      <c r="F325" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1348</v>
       </c>
@@ -14480,14 +14492,14 @@
       <c r="E326" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="F326" s="1">
-        <v>2</v>
+      <c r="F326" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1353</v>
       </c>
@@ -14503,14 +14515,14 @@
       <c r="E327" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="F327" s="1">
-        <v>3</v>
+      <c r="F327" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1358</v>
       </c>
@@ -14526,14 +14538,14 @@
       <c r="E328" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="F328" s="1">
-        <v>2</v>
+      <c r="F328" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1363</v>
       </c>
@@ -14549,14 +14561,14 @@
       <c r="E329" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="F329" s="1">
-        <v>3</v>
+      <c r="F329" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1368</v>
       </c>
@@ -14572,14 +14584,14 @@
       <c r="E330" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="F330" s="1">
-        <v>1</v>
+      <c r="F330" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1373</v>
       </c>
@@ -14595,14 +14607,14 @@
       <c r="E331" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="F331" s="1">
-        <v>3</v>
+      <c r="F331" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1378</v>
       </c>
@@ -14618,14 +14630,14 @@
       <c r="E332" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="F332" s="1">
-        <v>2</v>
+      <c r="F332" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1383</v>
       </c>
@@ -14641,14 +14653,14 @@
       <c r="E333" s="1" t="s">
         <v>1387</v>
       </c>
-      <c r="F333" s="1">
-        <v>3</v>
+      <c r="F333" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1388</v>
       </c>
@@ -14664,14 +14676,14 @@
       <c r="E334" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="F334" s="1">
-        <v>1</v>
+      <c r="F334" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1393</v>
       </c>
@@ -14687,14 +14699,14 @@
       <c r="E335" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="F335" s="1">
-        <v>2</v>
+      <c r="F335" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1398</v>
       </c>
@@ -14710,14 +14722,14 @@
       <c r="E336" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="F336" s="1">
-        <v>3</v>
+      <c r="F336" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1403</v>
       </c>
@@ -14733,14 +14745,14 @@
       <c r="E337" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="F337" s="1">
-        <v>1</v>
+      <c r="F337" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1408</v>
       </c>
@@ -14756,14 +14768,14 @@
       <c r="E338" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="F338" s="1">
-        <v>2</v>
+      <c r="F338" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1413</v>
       </c>
@@ -14779,14 +14791,14 @@
       <c r="E339" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="F339" s="1">
-        <v>2</v>
+      <c r="F339" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1418</v>
       </c>
@@ -14802,14 +14814,14 @@
       <c r="E340" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="F340" s="1">
-        <v>2</v>
+      <c r="F340" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1423</v>
       </c>
@@ -14825,14 +14837,14 @@
       <c r="E341" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="F341" s="1">
-        <v>3</v>
+      <c r="F341" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1428</v>
       </c>
@@ -14848,14 +14860,14 @@
       <c r="E342" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="F342" s="1">
-        <v>2</v>
+      <c r="F342" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1433</v>
       </c>
@@ -14871,14 +14883,14 @@
       <c r="E343" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="F343" s="1">
-        <v>4</v>
+      <c r="F343" t="s">
+        <v>2009</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1438</v>
       </c>
@@ -14894,14 +14906,14 @@
       <c r="E344" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="F344" s="1">
-        <v>2</v>
+      <c r="F344" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1442</v>
       </c>
@@ -14917,14 +14929,14 @@
       <c r="E345" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="F345" s="1">
-        <v>2</v>
+      <c r="F345" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1447</v>
       </c>
@@ -14940,14 +14952,14 @@
       <c r="E346" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="F346" s="1">
-        <v>1</v>
+      <c r="F346" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1452</v>
       </c>
@@ -14963,14 +14975,14 @@
       <c r="E347" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="F347" s="1">
-        <v>1</v>
+      <c r="F347" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1457</v>
       </c>
@@ -14986,14 +14998,14 @@
       <c r="E348" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="F348" s="1">
-        <v>2</v>
+      <c r="F348" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1462</v>
       </c>
@@ -15009,14 +15021,14 @@
       <c r="E349" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="F349" s="1">
-        <v>3</v>
+      <c r="F349" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1467</v>
       </c>
@@ -15032,14 +15044,14 @@
       <c r="E350" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F350" s="1">
-        <v>4</v>
+      <c r="F350" t="s">
+        <v>2009</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1471</v>
       </c>
@@ -15055,14 +15067,14 @@
       <c r="E351" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="F351" s="1">
-        <v>2</v>
+      <c r="F351" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1476</v>
       </c>
@@ -15078,14 +15090,14 @@
       <c r="E352" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="F352" s="1">
-        <v>2</v>
+      <c r="F352" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="353" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1481</v>
       </c>
@@ -15101,14 +15113,14 @@
       <c r="E353" s="1" t="s">
         <v>1483</v>
       </c>
-      <c r="F353" s="1">
-        <v>4</v>
+      <c r="F353" t="s">
+        <v>2009</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="354" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1486</v>
       </c>
@@ -15124,14 +15136,14 @@
       <c r="E354" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="F354" s="1">
-        <v>2</v>
+      <c r="F354" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="355" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1491</v>
       </c>
@@ -15147,14 +15159,14 @@
       <c r="E355" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="F355" s="1">
-        <v>2</v>
+      <c r="F355" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="356" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1496</v>
       </c>
@@ -15170,14 +15182,14 @@
       <c r="E356" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="F356" s="1">
-        <v>3</v>
+      <c r="F356" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="357" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1501</v>
       </c>
@@ -15193,14 +15205,14 @@
       <c r="E357" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="F357" s="1">
-        <v>2</v>
+      <c r="F357" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="358" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1506</v>
       </c>
@@ -15216,14 +15228,14 @@
       <c r="E358" s="1" t="s">
         <v>1510</v>
       </c>
-      <c r="F358" s="1">
-        <v>4</v>
+      <c r="F358" t="s">
+        <v>2009</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="359" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1511</v>
       </c>
@@ -15239,14 +15251,14 @@
       <c r="E359" s="1" t="s">
         <v>1515</v>
       </c>
-      <c r="F359" s="1">
-        <v>1</v>
+      <c r="F359" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="360" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1516</v>
       </c>
@@ -15262,14 +15274,14 @@
       <c r="E360" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="F360" s="1">
-        <v>3</v>
+      <c r="F360" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="361" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1521</v>
       </c>
@@ -15285,14 +15297,14 @@
       <c r="E361" s="1" t="s">
         <v>1525</v>
       </c>
-      <c r="F361" s="1">
-        <v>2</v>
+      <c r="F361" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="362" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1526</v>
       </c>
@@ -15308,14 +15320,14 @@
       <c r="E362" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="F362" s="1">
-        <v>1</v>
+      <c r="F362" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="363" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1531</v>
       </c>
@@ -15331,14 +15343,14 @@
       <c r="E363" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="F363" s="1">
-        <v>2</v>
+      <c r="F363" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="364" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1536</v>
       </c>
@@ -15354,14 +15366,14 @@
       <c r="E364" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="F364" s="1">
-        <v>2</v>
+      <c r="F364" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="365" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1541</v>
       </c>
@@ -15377,14 +15389,14 @@
       <c r="E365" s="1" t="s">
         <v>1545</v>
       </c>
-      <c r="F365" s="1">
-        <v>2</v>
+      <c r="F365" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="366" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1546</v>
       </c>
@@ -15400,14 +15412,14 @@
       <c r="E366" s="1" t="s">
         <v>1548</v>
       </c>
-      <c r="F366" s="1">
-        <v>4</v>
+      <c r="F366" t="s">
+        <v>2009</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="367" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1551</v>
       </c>
@@ -15423,15 +15435,15 @@
       <c r="E367" s="1" t="s">
         <v>1555</v>
       </c>
-      <c r="F367" s="1">
-        <v>3</v>
+      <c r="F367" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>1621</v>
       </c>
       <c r="XFC367" s="1"/>
     </row>
-    <row r="368" spans="1:7 16383:16383" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7 16383:16383" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1556</v>
       </c>
@@ -15447,14 +15459,14 @@
       <c r="E368" s="1" t="s">
         <v>1560</v>
       </c>
-      <c r="F368" s="1">
-        <v>2</v>
+      <c r="F368" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1561</v>
       </c>
@@ -15470,14 +15482,14 @@
       <c r="E369" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="F369" s="1">
-        <v>1</v>
+      <c r="F369" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1566</v>
       </c>
@@ -15493,14 +15505,14 @@
       <c r="E370" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="F370" s="1">
-        <v>3</v>
+      <c r="F370" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1571</v>
       </c>
@@ -15516,14 +15528,14 @@
       <c r="E371" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="F371" s="1">
-        <v>2</v>
+      <c r="F371" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1576</v>
       </c>
@@ -15539,14 +15551,14 @@
       <c r="E372" s="1" t="s">
         <v>1580</v>
       </c>
-      <c r="F372" s="1">
-        <v>3</v>
+      <c r="F372" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1581</v>
       </c>
@@ -15562,14 +15574,14 @@
       <c r="E373" s="1" t="s">
         <v>1585</v>
       </c>
-      <c r="F373" s="1">
-        <v>2</v>
+      <c r="F373" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1586</v>
       </c>
@@ -15585,14 +15597,14 @@
       <c r="E374" s="1" t="s">
         <v>1588</v>
       </c>
-      <c r="F374" s="1">
-        <v>4</v>
+      <c r="F374" t="s">
+        <v>2009</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1591</v>
       </c>
@@ -15608,14 +15620,14 @@
       <c r="E375" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="F375" s="1">
-        <v>3</v>
+      <c r="F375" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1596</v>
       </c>
@@ -15631,14 +15643,14 @@
       <c r="E376" s="1" t="s">
         <v>1600</v>
       </c>
-      <c r="F376" s="1">
-        <v>1</v>
+      <c r="F376" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1601</v>
       </c>
@@ -15654,14 +15666,14 @@
       <c r="E377" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="F377" s="1">
-        <v>1</v>
+      <c r="F377" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1606</v>
       </c>
@@ -15677,14 +15689,14 @@
       <c r="E378" s="1" t="s">
         <v>1610</v>
       </c>
-      <c r="F378" s="1">
-        <v>2</v>
+      <c r="F378" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1611</v>
       </c>
@@ -15700,14 +15712,14 @@
       <c r="E379" s="1" t="s">
         <v>1615</v>
       </c>
-      <c r="F379" s="1">
-        <v>2</v>
+      <c r="F379" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1616</v>
       </c>
@@ -15723,14 +15735,14 @@
       <c r="E380" s="1" t="s">
         <v>1620</v>
       </c>
-      <c r="F380" s="1">
-        <v>2</v>
+      <c r="F380" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1821</v>
       </c>
@@ -15746,14 +15758,14 @@
       <c r="E381" s="1" t="s">
         <v>1825</v>
       </c>
-      <c r="F381" s="1">
-        <v>2</v>
+      <c r="F381" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1826</v>
       </c>
@@ -15769,14 +15781,14 @@
       <c r="E382" s="1" t="s">
         <v>1830</v>
       </c>
-      <c r="F382" s="1">
-        <v>3</v>
+      <c r="F382" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1831</v>
       </c>
@@ -15792,14 +15804,14 @@
       <c r="E383" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F383" s="1">
-        <v>3</v>
+      <c r="F383" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1835</v>
       </c>
@@ -15815,14 +15827,14 @@
       <c r="E384" s="1" t="s">
         <v>1839</v>
       </c>
-      <c r="F384" s="1">
-        <v>3</v>
+      <c r="F384" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1840</v>
       </c>
@@ -15838,14 +15850,14 @@
       <c r="E385" s="1" t="s">
         <v>1843</v>
       </c>
-      <c r="F385" s="1">
-        <v>4</v>
+      <c r="F385" t="s">
+        <v>2009</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1844</v>
       </c>
@@ -15861,14 +15873,14 @@
       <c r="E386" s="1" t="s">
         <v>1847</v>
       </c>
-      <c r="F386" s="1">
-        <v>3</v>
+      <c r="F386" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1848</v>
       </c>
@@ -15884,14 +15896,14 @@
       <c r="E387" s="1" t="s">
         <v>1852</v>
       </c>
-      <c r="F387" s="1">
-        <v>2</v>
+      <c r="F387" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1853</v>
       </c>
@@ -15907,14 +15919,14 @@
       <c r="E388" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F388" s="1">
-        <v>2</v>
+      <c r="F388" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1854</v>
       </c>
@@ -15930,14 +15942,14 @@
       <c r="E389" s="1" t="s">
         <v>1858</v>
       </c>
-      <c r="F389" s="1">
-        <v>3</v>
+      <c r="F389" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1859</v>
       </c>
@@ -15953,14 +15965,14 @@
       <c r="E390" s="1" t="s">
         <v>1863</v>
       </c>
-      <c r="F390" s="1">
-        <v>3</v>
+      <c r="F390" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1864</v>
       </c>
@@ -15976,14 +15988,14 @@
       <c r="E391" s="1" t="s">
         <v>1868</v>
       </c>
-      <c r="F391" s="1">
-        <v>1</v>
+      <c r="F391" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1869</v>
       </c>
@@ -15999,14 +16011,14 @@
       <c r="E392" s="1" t="s">
         <v>1873</v>
       </c>
-      <c r="F392" s="1">
-        <v>2</v>
+      <c r="F392" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1874</v>
       </c>
@@ -16022,14 +16034,14 @@
       <c r="E393" s="1" t="s">
         <v>1878</v>
       </c>
-      <c r="F393" s="1">
-        <v>3</v>
+      <c r="F393" s="1" t="s">
+        <v>2008</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1879</v>
       </c>
@@ -16045,14 +16057,14 @@
       <c r="E394" s="1" t="s">
         <v>1881</v>
       </c>
-      <c r="F394" s="1">
-        <v>2</v>
+      <c r="F394" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1882</v>
       </c>
@@ -16068,14 +16080,14 @@
       <c r="E395" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F395" s="1">
-        <v>1</v>
+      <c r="F395" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1622</v>
       </c>
@@ -16091,14 +16103,14 @@
       <c r="E396" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="F396" s="1">
-        <v>2</v>
+      <c r="F396" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1627</v>
       </c>
@@ -16114,14 +16126,14 @@
       <c r="E397" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="F397" s="1">
-        <v>2</v>
+      <c r="F397" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1632</v>
       </c>
@@ -16137,14 +16149,14 @@
       <c r="E398" s="1" t="s">
         <v>1636</v>
       </c>
-      <c r="F398" s="1">
-        <v>2</v>
+      <c r="F398" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1637</v>
       </c>
@@ -16160,14 +16172,14 @@
       <c r="E399" s="1" t="s">
         <v>1641</v>
       </c>
-      <c r="F399" s="1">
-        <v>2</v>
+      <c r="F399" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1642</v>
       </c>
@@ -16183,14 +16195,14 @@
       <c r="E400" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="F400" s="1">
-        <v>2</v>
+      <c r="F400" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1647</v>
       </c>
@@ -16206,14 +16218,14 @@
       <c r="E401" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="F401" s="1">
-        <v>1</v>
+      <c r="F401" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1652</v>
       </c>
@@ -16229,14 +16241,14 @@
       <c r="E402" s="1" t="s">
         <v>1656</v>
       </c>
-      <c r="F402" s="1">
-        <v>2</v>
+      <c r="F402" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1657</v>
       </c>
@@ -16252,14 +16264,14 @@
       <c r="E403" s="1" t="s">
         <v>1661</v>
       </c>
-      <c r="F403" s="1">
-        <v>2</v>
+      <c r="F403" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1662</v>
       </c>
@@ -16275,14 +16287,14 @@
       <c r="E404" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="F404" s="1">
-        <v>2</v>
+      <c r="F404" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1667</v>
       </c>
@@ -16298,14 +16310,14 @@
       <c r="E405" s="1" t="s">
         <v>1671</v>
       </c>
-      <c r="F405" s="1">
-        <v>2</v>
+      <c r="F405" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1672</v>
       </c>
@@ -16321,14 +16333,14 @@
       <c r="E406" s="1" t="s">
         <v>1676</v>
       </c>
-      <c r="F406" s="1">
-        <v>2</v>
+      <c r="F406" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1677</v>
       </c>
@@ -16344,14 +16356,14 @@
       <c r="E407" s="1" t="s">
         <v>1681</v>
       </c>
-      <c r="F407" s="1">
-        <v>2</v>
+      <c r="F407" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1682</v>
       </c>
@@ -16367,14 +16379,14 @@
       <c r="E408" s="1" t="s">
         <v>1686</v>
       </c>
-      <c r="F408" s="1">
-        <v>2</v>
+      <c r="F408" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1687</v>
       </c>
@@ -16390,14 +16402,14 @@
       <c r="E409" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="F409" s="1">
-        <v>2</v>
+      <c r="F409" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1692</v>
       </c>
@@ -16413,14 +16425,14 @@
       <c r="E410" s="1" t="s">
         <v>1696</v>
       </c>
-      <c r="F410" s="1">
-        <v>2</v>
+      <c r="F410" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1697</v>
       </c>
@@ -16436,14 +16448,14 @@
       <c r="E411" s="1" t="s">
         <v>1701</v>
       </c>
-      <c r="F411" s="1">
-        <v>1</v>
+      <c r="F411" s="1" t="s">
+        <v>2006</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1702</v>
       </c>
@@ -16459,14 +16471,14 @@
       <c r="E412" s="1" t="s">
         <v>1706</v>
       </c>
-      <c r="F412" s="1">
-        <v>2</v>
+      <c r="F412" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1707</v>
       </c>
@@ -16482,14 +16494,14 @@
       <c r="E413" s="1" t="s">
         <v>1711</v>
       </c>
-      <c r="F413" s="1">
-        <v>2</v>
+      <c r="F413" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1712</v>
       </c>
@@ -16505,14 +16517,14 @@
       <c r="E414" s="1" t="s">
         <v>1716</v>
       </c>
-      <c r="F414" s="1">
-        <v>2</v>
+      <c r="F414" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1717</v>
       </c>
@@ -16528,14 +16540,14 @@
       <c r="E415" s="1" t="s">
         <v>1721</v>
       </c>
-      <c r="F415" s="1">
-        <v>2</v>
+      <c r="F415" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1722</v>
       </c>
@@ -16551,14 +16563,14 @@
       <c r="E416" s="1" t="s">
         <v>1726</v>
       </c>
-      <c r="F416" s="1">
-        <v>2</v>
+      <c r="F416" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1727</v>
       </c>
@@ -16574,14 +16586,14 @@
       <c r="E417" s="1" t="s">
         <v>1731</v>
       </c>
-      <c r="F417" s="1">
-        <v>2</v>
+      <c r="F417" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1732</v>
       </c>
@@ -16597,14 +16609,14 @@
       <c r="E418" s="1" t="s">
         <v>1736</v>
       </c>
-      <c r="F418" s="1">
-        <v>2</v>
+      <c r="F418" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1737</v>
       </c>
@@ -16620,14 +16632,14 @@
       <c r="E419" s="1" t="s">
         <v>1741</v>
       </c>
-      <c r="F419" s="1">
-        <v>2</v>
+      <c r="F419" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1742</v>
       </c>
@@ -16643,14 +16655,14 @@
       <c r="E420" s="1" t="s">
         <v>1746</v>
       </c>
-      <c r="F420" s="1">
-        <v>2</v>
+      <c r="F420" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1747</v>
       </c>
@@ -16666,14 +16678,14 @@
       <c r="E421" s="1" t="s">
         <v>1750</v>
       </c>
-      <c r="F421" s="1">
-        <v>2</v>
+      <c r="F421" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1751</v>
       </c>
@@ -16689,14 +16701,14 @@
       <c r="E422" s="1" t="s">
         <v>1755</v>
       </c>
-      <c r="F422" s="1">
-        <v>2</v>
+      <c r="F422" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1756</v>
       </c>
@@ -16712,14 +16724,14 @@
       <c r="E423" s="1" t="s">
         <v>1760</v>
       </c>
-      <c r="F423" s="1">
-        <v>2</v>
+      <c r="F423" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1761</v>
       </c>
@@ -16735,14 +16747,14 @@
       <c r="E424" s="1" t="s">
         <v>1765</v>
       </c>
-      <c r="F424" s="1">
-        <v>2</v>
+      <c r="F424" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1766</v>
       </c>
@@ -16758,14 +16770,14 @@
       <c r="E425" s="1" t="s">
         <v>1770</v>
       </c>
-      <c r="F425" s="1">
-        <v>2</v>
+      <c r="F425" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1771</v>
       </c>
@@ -16781,14 +16793,14 @@
       <c r="E426" s="1" t="s">
         <v>1775</v>
       </c>
-      <c r="F426" s="1">
-        <v>2</v>
+      <c r="F426" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1776</v>
       </c>
@@ -16804,14 +16816,14 @@
       <c r="E427" s="1" t="s">
         <v>1780</v>
       </c>
-      <c r="F427" s="1">
-        <v>2</v>
+      <c r="F427" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1781</v>
       </c>
@@ -16827,14 +16839,14 @@
       <c r="E428" s="1" t="s">
         <v>1785</v>
       </c>
-      <c r="F428" s="1">
-        <v>2</v>
+      <c r="F428" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1786</v>
       </c>
@@ -16850,14 +16862,14 @@
       <c r="E429" s="1" t="s">
         <v>1790</v>
       </c>
-      <c r="F429" s="1">
-        <v>2</v>
+      <c r="F429" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1791</v>
       </c>
@@ -16873,14 +16885,14 @@
       <c r="E430" s="1" t="s">
         <v>1795</v>
       </c>
-      <c r="F430" s="1">
-        <v>2</v>
+      <c r="F430" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1796</v>
       </c>
@@ -16896,14 +16908,14 @@
       <c r="E431" s="1" t="s">
         <v>1800</v>
       </c>
-      <c r="F431" s="1">
-        <v>2</v>
+      <c r="F431" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1801</v>
       </c>
@@ -16919,14 +16931,14 @@
       <c r="E432" s="1" t="s">
         <v>1805</v>
       </c>
-      <c r="F432" s="1">
-        <v>2</v>
+      <c r="F432" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1806</v>
       </c>
@@ -16942,14 +16954,14 @@
       <c r="E433" s="1" t="s">
         <v>1810</v>
       </c>
-      <c r="F433" s="1">
-        <v>2</v>
+      <c r="F433" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1811</v>
       </c>
@@ -16965,14 +16977,14 @@
       <c r="E434" s="1" t="s">
         <v>1815</v>
       </c>
-      <c r="F434" s="1">
-        <v>2</v>
+      <c r="F434" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1816</v>
       </c>
@@ -16988,14 +17000,19 @@
       <c r="E435" s="1" t="s">
         <v>1820</v>
       </c>
-      <c r="F435" s="1">
-        <v>2</v>
+      <c r="F435" s="1" t="s">
+        <v>2007</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G435" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
